--- a/data/trans_dic/P42-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P42-Estudios-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,22 +518,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido alguna vez al ginecólogo</t>
+          <t>Población que ha acudido alguna vez al ginecólogo (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,20 +537,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -595,26 +583,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -631,10 +599,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,22 +613,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,26 +647,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>84,93%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>74,98%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>85,18%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>83,98%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>84,93%</t>
         </is>
@@ -717,62 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>72,61; 77,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>83,34; 87,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>81,27; 86,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>82,34; 87,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,61; 77,62</t>
+          <t>72,61; 77,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,2; 87,23</t>
+          <t>83,34; 87,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,35; 86,25</t>
+          <t>81,27; 86,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>82,46; 87,05</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>72,61; 77,62</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>83,2; 87,23</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>81,35; 86,25</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>82,46; 87,05</t>
+          <t>82,34; 87,02</t>
         </is>
       </c>
     </row>
@@ -789,22 +713,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,26 +747,6 @@
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>73,54%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>79,91%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>87,42%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>87,28%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>73,54%</t>
         </is>
@@ -857,62 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>77,81; 81,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,62; 88,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,67; 88,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,88; 84,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>77,75; 81,72</t>
+          <t>77,81; 81,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,66; 88,92</t>
+          <t>85,62; 88,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,66; 88,76</t>
+          <t>85,67; 88,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>49,33; 84,5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>77,75; 81,72</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>85,66; 88,92</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>85,66; 88,76</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>49,33; 84,5</t>
+          <t>47,88; 84,45</t>
         </is>
       </c>
     </row>
@@ -929,22 +813,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,26 +847,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>88,81%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>87,79%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>92,09%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>92,56%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,81%</t>
         </is>
@@ -997,62 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>84,78; 90,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>89,05; 94,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,09; 94,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,95; 91,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>84,73; 90,56</t>
+          <t>84,78; 90,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,25; 94,54</t>
+          <t>89,05; 94,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,16; 94,67</t>
+          <t>90,09; 94,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85,75; 91,49</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>84,73; 90,56</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>89,25; 94,54</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>90,16; 94,67</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>85,75; 91,49</t>
+          <t>85,95; 91,51</t>
         </is>
       </c>
     </row>
@@ -1069,22 +913,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,26 +947,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>78,51%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>79,11%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>87,18%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>87,18%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>78,51%</t>
         </is>
@@ -1137,62 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>77,58; 80,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,07; 88,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,01; 88,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>60,09; 85,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,74; 80,45</t>
+          <t>77,58; 80,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,03; 88,38</t>
+          <t>86,07; 88,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,96; 88,23</t>
+          <t>86,01; 88,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59,92; 85,22</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>77,74; 80,45</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>86,03; 88,38</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>85,96; 88,23</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>59,92; 85,22</t>
+          <t>60,09; 85,28</t>
         </is>
       </c>
     </row>
@@ -1204,15 +1008,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1224,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1237,22 +1040,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido alguna vez al ginecólogo</t>
+          <t>Población que ha acudido alguna vez al ginecólogo (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,20 +1059,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1314,26 +1105,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1350,10 +1121,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1368,22 +1135,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>966</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>989</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1402,26 +1169,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>989</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>966</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1060</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>746</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>989</t>
         </is>
@@ -1436,22 +1183,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>978538</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1136152</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>826185</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>519554</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1470,26 +1217,6 @@
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>519554</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>978538</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1136152</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>826185</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>519554</t>
         </is>
@@ -1504,62 +1231,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>947618; 1011969</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1111565; 1163214</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>799587; 849638</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>503659; 532290</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>947588; 1012962</t>
+          <t>947618; 1011969</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1109638; 1163401</t>
+          <t>1111565; 1163214</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>800365; 848559</t>
+          <t>799587; 849638</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>504420; 532523</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>947588; 1012962</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1109638; 1163401</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>800365; 848559</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>504420; 532523</t>
+          <t>503659; 532290</t>
         </is>
       </c>
     </row>
@@ -1576,22 +1283,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1610,26 +1317,6 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1878</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1406</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1643</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1878</t>
         </is>
@@ -1644,22 +1331,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1265618</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1522734</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1724120</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1285438</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1678,26 +1365,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1285438</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1265618</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1522734</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1724120</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1285438</t>
         </is>
@@ -1712,62 +1379,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1232370; 1297471</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1491385; 1547524</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1692272; 1753381</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>837002; 1476166</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1231440; 1294354</t>
+          <t>1232370; 1297471</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1492059; 1548819</t>
+          <t>1491385; 1547524</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1692146; 1753309</t>
+          <t>1692272; 1753381</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>862224; 1477026</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1231440; 1294354</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>1492059; 1548819</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1692146; 1753309</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>862224; 1477026</t>
+          <t>837002; 1476166</t>
         </is>
       </c>
     </row>
@@ -1784,22 +1431,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>394</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>378</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>483</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>645</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1818,26 +1465,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>645</t>
         </is>
@@ -1852,22 +1479,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>417199</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>421344</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>505882</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>408963</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1886,26 +1513,6 @@
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>408963</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>417199</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>421344</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>505882</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>408963</t>
         </is>
@@ -1920,62 +1527,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>402904; 430196</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>407452; 431948</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>492355; 516838</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>395784; 421380</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>402668; 430391</t>
+          <t>402904; 430196</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>408356; 432556</t>
+          <t>407452; 431948</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>492781; 517410</t>
+          <t>492355; 516838</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>394873; 421283</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>402668; 430391</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>408356; 432556</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>492781; 517410</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>394873; 421283</t>
+          <t>395784; 421380</t>
         </is>
       </c>
     </row>
@@ -1992,22 +1579,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2026,26 +1613,6 @@
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3512</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2584</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2844</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2872</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3512</t>
         </is>
@@ -2060,22 +1627,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2661356</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3080230</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3056188</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2213955</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2094,26 +1661,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2213955</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2661356</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3080230</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3056188</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2213955</t>
         </is>
@@ -2128,62 +1675,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2609848; 2707448</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3040809; 3118884</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3015170; 3094909</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1694699; 2405115</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2615119; 2706419</t>
+          <t>2609848; 2707448</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3039686; 3122716</t>
+          <t>3040809; 3118884</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3013638; 3093018</t>
+          <t>3015170; 3094909</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1689695; 2403283</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>2615119; 2706419</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>3039686; 3122716</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>3013638; 3093018</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>1689695; 2403283</t>
+          <t>1694699; 2405115</t>
         </is>
       </c>
     </row>
@@ -2195,14 +1722,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P42-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P42-Estudios-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,56%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72,61; 77,54</t>
+          <t>72,59; 77,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,34; 87,21</t>
+          <t>83,12; 87,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,27; 86,36</t>
+          <t>81,22; 86,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82,34; 87,02</t>
+          <t>82,22; 86,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,61; 77,54</t>
+          <t>72,59; 77,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,34; 87,21</t>
+          <t>83,12; 87,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,27; 86,36</t>
+          <t>81,22; 86,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>82,34; 87,02</t>
+          <t>82,22; 86,82</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>81,5%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>77,81; 81,92</t>
+          <t>78,01; 81,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,62; 88,85</t>
+          <t>85,81; 88,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,67; 88,76</t>
+          <t>85,87; 88,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47,88; 84,45</t>
+          <t>79,3; 83,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>77,81; 81,92</t>
+          <t>78,01; 81,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,62; 88,85</t>
+          <t>85,81; 88,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,67; 88,76</t>
+          <t>85,87; 88,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,88; 84,45</t>
+          <t>79,3; 83,6</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,47%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84,78; 90,52</t>
+          <t>84,87; 90,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,05; 94,4</t>
+          <t>88,83; 94,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90,09; 94,56</t>
+          <t>90,0; 94,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85,95; 91,51</t>
+          <t>86,38; 91,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>84,78; 90,52</t>
+          <t>84,87; 90,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,05; 94,4</t>
+          <t>88,83; 94,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,09; 94,56</t>
+          <t>90,0; 94,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85,95; 91,51</t>
+          <t>86,38; 91,79</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77,58; 80,48</t>
+          <t>77,69; 80,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>86,07; 88,28</t>
+          <t>85,99; 88,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86,01; 88,28</t>
+          <t>86,07; 88,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60,09; 85,28</t>
+          <t>81,98; 84,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,58; 80,48</t>
+          <t>77,69; 80,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,07; 88,28</t>
+          <t>85,99; 88,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,01; 88,28</t>
+          <t>86,07; 88,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>60,09; 85,28</t>
+          <t>81,98; 84,96</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>519554</t>
+          <t>563565</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>519554</t>
+          <t>563565</t>
         </is>
       </c>
     </row>
@@ -1231,42 +1231,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>947618; 1011969</t>
+          <t>947334; 1008863</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1111565; 1163214</t>
+          <t>1108607; 1164010</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>799587; 849638</t>
+          <t>799083; 848180</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>503659; 532290</t>
+          <t>547953; 578603</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>947618; 1011969</t>
+          <t>947334; 1008863</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1111565; 1163214</t>
+          <t>1108607; 1164010</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>799587; 849638</t>
+          <t>799083; 848180</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>503659; 532290</t>
+          <t>547953; 578603</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1285438</t>
+          <t>1318909</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1285438</t>
+          <t>1318909</t>
         </is>
       </c>
     </row>
@@ -1379,42 +1379,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1232370; 1297471</t>
+          <t>1235521; 1294419</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1491385; 1547524</t>
+          <t>1494645; 1549831</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1692272; 1753381</t>
+          <t>1696209; 1754572</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>837002; 1476166</t>
+          <t>1283290; 1352850</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1232370; 1297471</t>
+          <t>1235521; 1294419</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1491385; 1547524</t>
+          <t>1494645; 1549831</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1692272; 1753381</t>
+          <t>1696209; 1754572</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>837002; 1476166</t>
+          <t>1283290; 1352850</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>408963</t>
+          <t>456686</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>408963</t>
+          <t>456686</t>
         </is>
       </c>
     </row>
@@ -1527,42 +1527,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>402904; 430196</t>
+          <t>403355; 429480</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>407452; 431948</t>
+          <t>406431; 431366</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>492355; 516838</t>
+          <t>491910; 516673</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>395784; 421380</t>
+          <t>440882; 468515</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>402904; 430196</t>
+          <t>403355; 429480</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>407452; 431948</t>
+          <t>406431; 431366</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>492355; 516838</t>
+          <t>491910; 516673</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>395784; 421380</t>
+          <t>440882; 468515</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2213955</t>
+          <t>2339159</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2213955</t>
+          <t>2339159</t>
         </is>
       </c>
     </row>
@@ -1675,42 +1675,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2609848; 2707448</t>
+          <t>2613736; 2708203</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3040809; 3118884</t>
+          <t>3037974; 3116951</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3015170; 3094909</t>
+          <t>3017409; 3096773</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1694699; 2405115</t>
+          <t>2291424; 2374868</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2609848; 2707448</t>
+          <t>2613736; 2708203</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3040809; 3118884</t>
+          <t>3037974; 3116951</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3015170; 3094909</t>
+          <t>3017409; 3096773</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1694699; 2405115</t>
+          <t>2291424; 2374868</t>
         </is>
       </c>
     </row>
